--- a/examples/Import téléphones pour test.xlsx
+++ b/examples/Import téléphones pour test.xlsx
@@ -73,7 +73,7 @@
     <t xml:space="preserve">Oppo A73</t>
   </si>
   <si>
-    <t xml:space="preserve">Silver </t>
+    <t xml:space="preserve">Bleu</t>
   </si>
   <si>
     <t xml:space="preserve">Neuf</t>
@@ -377,7 +377,7 @@
         <v>16</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>17</v>
@@ -396,7 +396,7 @@
         <v>1300000</v>
       </c>
       <c r="J2" s="12" t="n">
-        <v>863038050322755</v>
+        <v>863038050322748</v>
       </c>
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
